--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_137_R14.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_137_R14.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5389</v>
+        <v>3.0107</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5758</v>
+        <v>2.0476</v>
       </c>
       <c r="F2" t="n">
         <v>0.9631</v>
@@ -610,10 +610,10 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3224</v>
+        <v>0.7943</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0553</v>
+        <v>0.5272</v>
       </c>
       <c r="U2" t="n">
         <v>0.2671</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2774</v>
+        <v>0.5706</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0637</v>
+        <v>-0.3526</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7863</v>
+        <v>0.9232</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5841</v>
+        <v>0.8377</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.0661</v>
+        <v>-0.2698</v>
       </c>
       <c r="I3" t="n">
-        <v>0.482</v>
+        <v>1.1075</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2075</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9068000000000001</v>
+        <v>0.1849</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6993</v>
+        <v>0.746</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3765</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1592</v>
+        <v>-0.4547</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2173</v>
+        <v>0.3615</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6959</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q3" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7834</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4155</v>
+        <v>-0.0198</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4643</v>
+        <v>0.0514</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0488</v>
+        <v>-0.0712</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2862</v>
+        <v>2.1444</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>D. DAVIDOVAC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1834</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5771</v>
+        <v>0.311</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3937</v>
+        <v>0.2448</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.0461</v>
+        <v>-0.2186</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0888</v>
+        <v>0.0457</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.9573</v>
+        <v>-0.2643</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.0488</v>
+        <v>0.0672</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3767</v>
+        <v>0.0672</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.4255</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9973</v>
+        <v>-0.2859</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4655</v>
+        <v>-0.0216</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5319</v>
+        <v>-0.2643</v>
       </c>
       <c r="P4" t="n">
         <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0877</v>
+        <v>-0.1533</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5716</v>
+        <v>0.2438</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.4839</v>
+        <v>-0.3971</v>
       </c>
       <c r="V4" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. DAVIDOVAC</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3199</v>
+        <v>0.2294</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0751</v>
+        <v>0.3543</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2448</v>
+        <v>-0.1249</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2186</v>
+        <v>-2.0461</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0457</v>
+        <v>-0.0888</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2643</v>
+        <v>-1.9573</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0672</v>
+        <v>-1.0488</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0672</v>
+        <v>0.3767</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.4255</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2859</v>
+        <v>-0.9973</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0216</v>
+        <v>-0.4655</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2643</v>
+        <v>-0.5319</v>
       </c>
       <c r="P5" t="n">
         <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3892</v>
+        <v>0.1338</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.3489</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3971</v>
+        <v>-1.2151</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1915</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.135</v>
+        <v>-0.2397</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3265</v>
+        <v>0.1643</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8377</v>
+        <v>-2.7124</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2698</v>
+        <v>-1.5413</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1075</v>
+        <v>-1.1711</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9308999999999999</v>
+        <v>-1.4183</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1849</v>
+        <v>-0.6687</v>
       </c>
       <c r="L6" t="n">
-        <v>0.746</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-1.2942</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4547</v>
+        <v>-0.8726</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3615</v>
+        <v>-0.4216</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3989</v>
+        <v>0.405</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.731</v>
+        <v>0.1063</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3321</v>
+        <v>0.2987</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>D. MOTIEJUNAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6817</v>
+        <v>-0.1036</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7116</v>
+        <v>-1.126</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0299</v>
+        <v>1.0224</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7124</v>
+        <v>-0.4614</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5413</v>
+        <v>-0.09</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1711</v>
+        <v>-0.3713</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4183</v>
+        <v>0.9614</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6687</v>
+        <v>0.9614</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2942</v>
+        <v>-1.4227</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8726</v>
+        <v>-1.0514</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4216</v>
+        <v>-0.3713</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2012</v>
+        <v>1.0537</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3655</v>
+        <v>0.2322</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1643</v>
+        <v>0.8215</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MOTIEJUNAS</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6933</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7157</v>
+        <v>-0.2207</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0224</v>
+        <v>-0.7527</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4614</v>
+        <v>-1.5841</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.09</v>
+        <v>-2.0661</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3713</v>
+        <v>0.482</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9614</v>
+        <v>-0.2075</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9614</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6993</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4227</v>
+        <v>-1.3765</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0514</v>
+        <v>-1.1592</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3713</v>
+        <v>-0.2173</v>
       </c>
       <c r="P8" t="n">
         <v>-0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>2.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4639</v>
+        <v>1.1648</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3576</v>
+        <v>1.1799</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8215</v>
+        <v>-0.0151</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.718</v>
+        <v>-1.5761</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3931</v>
+        <v>-1.3184</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3249</v>
+        <v>-0.2577</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8582</v>
@@ -1156,13 +1156,13 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4112</v>
+        <v>-0.2693</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2794</v>
+        <v>0.3541</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6906</v>
+        <v>-0.6234</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.95</v>
+        <v>-2.1683</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3081</v>
+        <v>-2.7616</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3581</v>
+        <v>0.5934</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6996</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3921</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4402</v>
+        <v>0.1063</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.952</v>
+        <v>-0.7167</v>
       </c>
       <c r="V10" t="n">
         <v>0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9958</v>
+        <v>-5.6242</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7361</v>
+        <v>-3.0284</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2597</v>
+        <v>-2.5957</v>
       </c>
       <c r="G11" t="n">
         <v>-6.0006</v>
@@ -1312,13 +1312,13 @@
         <v>3.0154</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6879</v>
+        <v>1.0596</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2952</v>
+        <v>1.0029</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3927</v>
+        <v>0.0567</v>
       </c>
       <c r="V11" t="n">
         <v>-2.5387</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.527699999999999</v>
+        <v>-6.1543</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.7079</v>
+        <v>-6.3345</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1801999999999997</v>
+        <v>0.1802000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-15.0271</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.1993</v>
+        <v>-3.199299999999999</v>
       </c>
       <c r="I12" t="n">
         <v>-11.8279</v>
@@ -1366,7 +1366,7 @@
         <v>-4.821099999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>3.544999999999999</v>
+        <v>3.545</v>
       </c>
       <c r="L12" t="n">
         <v>-8.3659</v>
@@ -1390,16 +1390,16 @@
         <v>18.5564</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1848</v>
+        <v>3.5584</v>
       </c>
       <c r="T12" t="n">
-        <v>4.779400000000001</v>
+        <v>5.153</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5947</v>
+        <v>-1.5946</v>
       </c>
       <c r="V12" t="n">
-        <v>2.9952</v>
+        <v>2.995199999999999</v>
       </c>
       <c r="W12" t="n">
         <v>9.5702</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5015</v>
+        <v>6.1584</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0768</v>
+        <v>4.6666</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4246</v>
+        <v>1.4918</v>
       </c>
       <c r="G13" t="n">
         <v>4.2221</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1871</v>
+        <v>0.4698</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2082</v>
+        <v>0.3815</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0211</v>
+        <v>0.0883</v>
       </c>
       <c r="V13" t="n">
         <v>1.4665</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4197</v>
+        <v>4.5045</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3286</v>
+        <v>2.243</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0911</v>
+        <v>2.2615</v>
       </c>
       <c r="G14" t="n">
-        <v>6.0374</v>
+        <v>-0.8608</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2461</v>
+        <v>-0.4525</v>
       </c>
       <c r="I14" t="n">
-        <v>4.7913</v>
+        <v>-0.4084</v>
       </c>
       <c r="J14" t="n">
-        <v>6.5493</v>
+        <v>-1.1353</v>
       </c>
       <c r="K14" t="n">
-        <v>2.541</v>
+        <v>0.5279</v>
       </c>
       <c r="L14" t="n">
-        <v>4.0082</v>
+        <v>-1.6633</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5119</v>
+        <v>0.2745</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2949</v>
+        <v>-0.9804</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7831</v>
+        <v>1.2549</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3917</v>
+        <v>2.5515</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4063</v>
+        <v>-0.5445</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8136</v>
+        <v>0.02</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4072</v>
+        <v>-0.5645</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8197</v>
+        <v>3.3584</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0722</v>
+        <v>3.3584</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.8919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8709</v>
+        <v>4.1395</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4174</v>
+        <v>4.0363</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4536</v>
+        <v>0.1032</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8608</v>
+        <v>6.0374</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4525</v>
+        <v>1.2461</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4084</v>
+        <v>4.7913</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1353</v>
+        <v>6.5493</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5279</v>
+        <v>2.541</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.6633</v>
+        <v>4.0082</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2745</v>
+        <v>-0.5119</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9804</v>
+        <v>-1.2949</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2549</v>
+        <v>0.7831</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.178</v>
+        <v>0.3134</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8057</v>
+        <v>-0.1059</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3724</v>
+        <v>0.4193</v>
       </c>
       <c r="V15" t="n">
-        <v>3.3584</v>
+        <v>-0.8197</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3584</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8824</v>
+        <v>3.0283</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1707</v>
+        <v>0.8784</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7117</v>
+        <v>2.1499</v>
       </c>
       <c r="G16" t="n">
         <v>1.1425</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9739</v>
+        <v>0.172</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2003</v>
+        <v>0.5074</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7736</v>
+        <v>-0.3354</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4917</v>
+        <v>0.1624</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0507</v>
+        <v>-0.0078</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5424</v>
+        <v>0.1701</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3858</v>
+        <v>-0.678</v>
       </c>
       <c r="H17" t="n">
-        <v>0.228</v>
+        <v>-0.3301</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1578</v>
+        <v>-0.348</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0472</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1576</v>
+        <v>0.0168</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1104</v>
+        <v>0.0736</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4329</v>
+        <v>-0.7684</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3856</v>
+        <v>-0.3469</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0474</v>
+        <v>-0.4216</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6241</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3882</v>
+        <v>-0.0982</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2359</v>
+        <v>0.0108</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3187</v>
+        <v>-0.1867</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5644</v>
+        <v>-1.0362</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8831</v>
+        <v>0.8495</v>
       </c>
       <c r="G18" t="n">
         <v>1.2376</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6146</v>
+        <v>0.1092</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4208</v>
+        <v>-0.051</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1937</v>
+        <v>0.1601</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1418</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2344</v>
+        <v>-0.3822</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6178</v>
+        <v>-0.8296</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3834</v>
+        <v>0.4474</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2066</v>
+        <v>1.411</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2701</v>
+        <v>0.3469</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0636</v>
+        <v>1.0641</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2827</v>
+        <v>1.3688</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3564</v>
+        <v>1.5061</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6391</v>
+        <v>-0.1373</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4893</v>
+        <v>0.0421</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0862</v>
+        <v>-1.1592</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5756</v>
+        <v>1.2014</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3917</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5639</v>
+        <v>-0.0277</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2923</v>
+        <v>0.2087</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7284</v>
+        <v>-0.2363</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0564</v>
+        <v>-0.7658</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1257</v>
+        <v>-1.2302</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0693</v>
+        <v>0.4644</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.678</v>
+        <v>1.3858</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3301</v>
+        <v>0.228</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.348</v>
+        <v>1.1578</v>
       </c>
       <c r="J20" t="n">
-        <v>0.09039999999999999</v>
+        <v>-0.0472</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0168</v>
+        <v>-0.1576</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>0.1104</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7684</v>
+        <v>1.4329</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3469</v>
+        <v>0.3856</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4216</v>
+        <v>1.0474</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3062</v>
+        <v>0.3666</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2161</v>
+        <v>0.2087</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0901</v>
+        <v>0.1579</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4501</v>
+        <v>-1.0681</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5373</v>
+        <v>-0.7976</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0872</v>
+        <v>-0.2705</v>
       </c>
       <c r="G21" t="n">
-        <v>1.411</v>
+        <v>0.2066</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3469</v>
+        <v>0.2701</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0641</v>
+        <v>-0.0636</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3688</v>
+        <v>-0.2827</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5061</v>
+        <v>0.3564</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1373</v>
+        <v>-0.6391</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0421</v>
+        <v>0.4893</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1592</v>
+        <v>-0.0862</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2014</v>
+        <v>0.5756</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-1.3917</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0956</v>
+        <v>0.2614</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4991</v>
+        <v>0.8768</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5966</v>
+        <v>-0.6155</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7425</v>
+        <v>-1.3735</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7086</v>
+        <v>-3.4727</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9661</v>
+        <v>2.0992</v>
       </c>
       <c r="G22" t="n">
         <v>4.4961</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.6872</v>
+        <v>-1.3181</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8215</v>
+        <v>-0.5856</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.8657</v>
+        <v>-0.7325</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9427</v>
+        <v>-4.5439</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.805</v>
+        <v>-4.6306</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1377</v>
+        <v>0.0867</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5731</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>0.847</v>
+        <v>0.2458</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0578</v>
+        <v>0.2322</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2109</v>
+        <v>0.0136</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1444</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.527600000000001</v>
+        <v>9.672900000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1803999999999988</v>
+        <v>-0.1804000000000014</v>
       </c>
       <c r="F24" t="n">
-        <v>6.708</v>
+        <v>9.853200000000001</v>
       </c>
       <c r="G24" t="n">
         <v>15.0272</v>
@@ -2302,10 +2302,10 @@
         <v>10.2062</v>
       </c>
       <c r="K24" t="n">
-        <v>6.744</v>
+        <v>6.744000000000002</v>
       </c>
       <c r="L24" t="n">
-        <v>3.461800000000001</v>
+        <v>3.4618</v>
       </c>
       <c r="M24" t="n">
         <v>4.8211</v>
@@ -2314,7 +2314,7 @@
         <v>-3.5448</v>
       </c>
       <c r="O24" t="n">
-        <v>8.3659</v>
+        <v>8.365900000000002</v>
       </c>
       <c r="P24" t="n">
         <v>-2.3196</v>
@@ -2326,16 +2326,16 @@
         <v>16.2368</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.184699999999999</v>
+        <v>-0.03950000000000012</v>
       </c>
       <c r="T24" t="n">
         <v>1.5946</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.779799999999999</v>
+        <v>-1.6342</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.9952</v>
+        <v>-2.995200000000001</v>
       </c>
       <c r="W24" t="n">
         <v>6.575000000000001</v>
